--- a/excel/shuwa_exam_question_list_ver0.04.xlsx
+++ b/excel/shuwa_exam_question_list_ver0.04.xlsx
@@ -15458,7 +15458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col width="9" customWidth="1" style="5" min="1" max="4"/>
@@ -18660,10 +18660,1011 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="409.5" customHeight="1"/>
-    <row r="71" ht="409.5" customHeight="1"/>
-    <row r="72" ht="409.5" customHeight="1"/>
-    <row r="73" ht="409.5" customHeight="1"/>
+    <row r="70" ht="409.5" customHeight="1">
+      <c r="A70">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>音の高さを表す単位はどれですか。</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1. ヘルツ
+2. デシベル
+3. ワット
+4. ルクス</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1. ヘルツ。音の高さ（周波数）はヘルツ（Hz）で表します。音の大きさ（強さ）を表すデシベル（dB）と混同しやすいので注意しましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="409.5" customHeight="1">
+      <c r="A71">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>音の3要素は「大きさ」「高さ」と、あと1つはどれですか。</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1. 速さ
+2. 長さ
+3. 音色
+4. 響き</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3. 音色。音の3要素は「大きさ（強さ）」「高さ」「音色」です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="409.5" customHeight="1">
+      <c r="A72">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>聴覚障害者を支援するために訓練された身体障害者補助犬はどれですか。</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1. 盲導犬
+2. 介助犬
+3. 聴導犬
+4. 警察犬</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3. 聴導犬。身体障害者補助犬法に定められた補助犬は盲導犬・介助犬・聴導犬の3種類で、聴導犬はチャイムや警報音などの生活音を聴覚障害者に知らせます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="409.5" customHeight="1">
+      <c r="A73">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>聞こえが不自由なことを表し、聴覚障害者が支援や配慮を必要としていることを周囲に示すマークはどれですか。</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1. 耳マーク
+2. ハートプラスマーク
+3. ヘルプマーク
+4. オストメイトマーク</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1. 耳マーク。耳の形をデザインしたマークで、聞こえない・聞こえにくい人が「耳が不自由です」と示したり、窓口などで筆談対応ができることを示すのに使われます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>補聴器や人工内耳の受信機能を利用して、磁気によって音声を直接届ける聴覚支援設備はどれですか。</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1. ヒアリングループ（磁気誘導ループ）
+2. スピーカー
+3. 集音器
+4. 骨伝導イヤホン</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1. ヒアリングループ（磁気誘導ループ）。床などに敷設したループ状のアンテナから磁気信号を送り、対応する補聴器等で雑音の少ない音声を聞くことができる設備で、公共施設などに設置が進んでいます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>全日本ろうあ連盟が結成された年はいつですか。</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1. 1947年
+2. 1955年
+3. 1964年
+4. 1981年</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1. 1947年。全日本ろうあ連盟は1947（昭和22）年に群馬県伊香保温泉で結成された、全国のろう者の当事者団体です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>第1回デフリンピック（当時は国際ろう者競技大会）が1924年に開催された都市はどこですか。</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1. ロンドン
+2. パリ
+3. ローマ
+4. ベルリン</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2. パリ。第1回大会は1924年にフランスのパリで開催されました。2025年には開催100周年の節目に、日本初開催となる東京大会が行われました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>日本が国連の障害者権利条約を批准した年はいつですか。</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1. 2006年
+2. 2011年
+3. 2014年
+4. 2020年</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3. 2014年。障害者権利条約は2006年に国連総会で採択され、日本は障害者基本法改正や障害者差別解消法制定など国内法を整備した上で2014（平成26）年に批准しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>障害者差別解消法が施行された年はいつですか。</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1. 2011年
+2. 2013年
+3. 2016年
+4. 2021年</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3. 2016年。障害者差別解消法は2013（平成25）年に成立し、2016（平成28）年4月に施行されました。不当な差別的取扱いの禁止と合理的配慮の提供を定めています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>改正障害者差別解消法により、2024年4月から民間事業者に義務化されたものはどれですか。</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1. 合理的配慮の提供
+2. 障害者の優先雇用
+3. 手話通訳者の常駐
+4. バリアフリー工事</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1. 合理的配慮の提供。それまで民間事業者は努力義務でしたが、2021年の法改正（2024年4月施行）により合理的配慮の提供が法的義務となりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>年齢や障害の有無にかかわらず、最初から誰もが使いやすいように製品や環境を設計する考え方はどれですか。</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1. バリアフリー
+2. ユニバーサルデザイン
+3. リハビリテーション
+4. アクセシビリティ</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2. ユニバーサルデザイン。既にある障壁を取り除くバリアフリーに対し、ユニバーサルデザインは初めから障壁を作らない設計思想です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>「障害のある人もない人も同じように当たり前の生活を送れる社会こそ正常な社会である」というノーマライゼーションの理念を提唱したバンク・ミケルセンの出身国はどこですか。</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1. スウェーデン
+2. デンマーク
+3. アメリカ
+4. イギリス</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2. デンマーク。バンク・ミケルセンはデンマークの行政官で、1950年代に知的障害者の親の会の運動を通じてノーマライゼーションの理念を提唱しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>「聴覚障害者等による電話の利用の円滑化に関する法律」が成立し、電話リレーサービスが公共インフラとして制度化された年はいつですか。</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1. 2013年
+2. 2016年
+3. 2020年
+4. 2024年</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>3. 2020年。同法は2020（令和2）年6月に成立し、2021（令和3）年7月から公共インフラとしての電話リレーサービスが開始されました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>日本で最初のろう学校といわれる京都盲唖院が設立された年はいつですか。</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1. 1868年
+2. 1878年
+3. 1898年
+4. 1908年</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2. 1878年。京都盲唖院は1878（明治11）年に古河太四郎らによって設立された、日本で最初のろう学校といわれています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>手話通訳士の資格認定試験（手話通訳技能認定試験）を実施している機関はどれですか。</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1. 聴力障害者情報文化センター
+2. 全国手話研修センター
+3. 日本財団
+4. 国立障害者リハビリテーションセンター</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1. 聴力障害者情報文化センター。手話通訳士試験は厚生労働大臣認定の資格試験で、社会福祉法人聴力障害者情報文化センターが実施しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>視覚と聴覚の両方に障害のある盲ろう者が、相手の手話の手の形や動きに触れて読み取るコミュニケーション方法はどれですか。</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1. 触手話
+2. 読話
+3. 空書
+4. 筆談</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1. 触手話。盲ろう者が相手の手に触れて手話を読み取る方法です。ほかに盲ろう者のコミュニケーション手段には指点字などがあります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>4択問題</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>世界ろう連盟の会議やデフリンピックなど、国際的な交流の場で主に使われる手話はどれですか。</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1. アメリカ手話
+2. 国際手話
+3. 日本手話
+4. イギリス手話</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2. 国際手話。手話は国や地域ごとに異なる言語ですが、国際的な場では国際手話が共通のコミュニケーション手段として使われています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>手話による教育は、フランスの（ア）が1760年にパリに設立したろう学校で系統化されました。日本では1878年に（イ）らが（ウ）を設立し、これが日本で最初のろう学校といわれています。</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1. ド・レペ
+2. グラハム・ベル
+3. 古河太四郎
+4. 大久保利通
+5. 京都盲唖院
+6. 東京聾唖学校
+7. 筑波技術大学
+8. 全国手話研修センター</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1,3,5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>正答: （ア）ド・レペ（イ）古河太四郎（ウ）京都盲唖院。ド・レペは世界初の公立ろう学校をパリに設立した人物、古河太四郎は1878年に京都盲唖院を設立した日本ろう教育の先駆者です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>障害者福祉制度は、2003年の（ア）の導入により行政が決定する「措置制度」から利用者が選ぶ「契約制度」へと転換しました。2006年には（イ）が施行され、2013年には（ウ）へと改正されて難病患者も支援の対象に加わりました。</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1. 支援費制度
+2. 障害者自立支援法
+3. 障害者総合支援法
+4. 介護保険制度
+5. 身体障害者福祉法
+6. 障害者雇用促進法
+7. 生活保護法
+8. 児童福祉法</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>正答: （ア）支援費制度（イ）障害者自立支援法（ウ）障害者総合支援法。支援費制度（2003）→障害者自立支援法（2006）→障害者総合支援法（2013）という変遷を押さえましょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>障害者権利条約は2006年12月の国連総会で採択されました。日本は国内法の整備を進めた上で（ア）年に批准しました。この条約は「私たちのことを私たち抜きに決めないで」を合言葉に作られ、障害のとらえ方として（イ）の視点に立ち、手話を（ウ）として位置づけています。</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1. 2008
+2. 2014
+3. 2020
+4. 医学モデル
+5. 社会モデル
+6. 言語
+7. 福祉サービス
+8. 身振り</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2,5,6</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>正答: （ア）2014（イ）社会モデル（ウ）言語。日本の批准は2014（平成26）年。条約第2条では手話が言語に含まれることが明記されています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2013年10月、（ア）が全国で初めて手話言語条例を制定しました。この条例では手話を（イ）として位置づけ、手話の（ウ）に関する施策を進めることを定めています。</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1. 鳥取県
+2. 北海道
+3. 東京都
+4. 言語
+5. 福祉的支援の手段
+6. 理解と普及
+7. 資格制度
+8. 届出制度</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1,4,6</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>正答: （ア）鳥取県（イ）言語（ウ）理解と普及。鳥取県手話言語条例は2013年10月に成立した全国初の手話言語条例で、手話を言語として認め、普及を進めることを定めています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>私たちは（ア）を使ってお互いの意思や感情を伝え合っていますが、表情や視線、身振りといった（イ）も大きな役割を果たしています。聞こえない人との会話では、話し手の口の動きから内容を読み取る（ウ）が使われることもあります。</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1. ことば
+2. 言語コミュニケーション
+3. 非言語コミュニケーション
+4. 読話
+5. 指文字
+6. 筆談
+7. 空書
+8. 触手話</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1,3,4</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>正答: （ア）ことば（イ）非言語コミュニケーション（ウ）読話。読話は口形から話の内容を読み取る方法ですが、正確に読み取れる割合には限界があるため、他の手段と組み合わせることが大切です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>準1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>穴埋め形式</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>毎年12月3日から9日までは（ア）です。初日の12月3日は国連が定めた（イ）でもあります。これらは障害者の福祉についての国民の（ウ）を深めることを目的としています。</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1. 障害者週間
+2. 人権週間
+3. 国際障害者デー
+4. 世界ろう者の日
+5. 関心と理解
+6. 監視と指導
+7. 義務と責任
+8. 訓練と指導</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1,3,5</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>正答: （ア）障害者週間（イ）国際障害者デー（ウ）関心と理解。障害者週間は障害者基本法に基づき毎年12月3日〜9日に実施され、12月3日は国連の国際障害者デーです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>模擬A</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>小論文</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>「聴覚障害者が働きやすい職場にするために、周囲の人や企業にはどのような配慮や工夫が求められると考えますか。あなたの考えを述べてください。」</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>- 序論（導入）
+  - 職場における情報保障・合理的配慮の重要性を簡潔に述べる
+  - 例：「会議や朝礼など音声中心の情報共有は、聴覚障害者にとって大きな障壁となる」
+- 本論（具体策）
+  - 情報保障の工夫：筆談・チャットツール・音声認識アプリ・手話通訳や要約筆記の活用
+  - 環境づくり：話すときは顔を見て話す、複数人が同時に話さない、視覚的な資料を用意する
+  - 制度面：合理的配慮の提供義務（2024年4月から民間事業者も義務化）、社内研修や手話学習の機会
+- 結論（まとめ）
+  - 配慮は特別扱いではなく、誰もが力を発揮できる職場づくりにつながることを述べる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I65"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/shuwa_exam_question_list_ver0.04.xlsx
+++ b/excel/shuwa_exam_question_list_ver0.04.xlsx
@@ -12892,7 +12892,7 @@
       </c>
       <c r="I263" s="1" t="inlineStr">
         <is>
-          <t>nrWSd_Viugk</t>
+          <t>nrWSd_VIugk</t>
         </is>
       </c>
       <c r="J263" s="14" t="inlineStr">
